--- a/schedule-engine/samples/Demo_Update_Workbook.xlsx
+++ b/schedule-engine/samples/Demo_Update_Workbook.xlsx
@@ -11,21 +11,22 @@
     <sheet sheetId="5" name="Update Sheet" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Look-ahead" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Attention" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Health Check" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Change Log" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Relationships" state="visible" r:id="rId13"/>
+    <sheet sheetId="8" name="Concerns" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Health Check" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Change Log" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Relationships" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3477" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3558" uniqueCount="404">
   <si>
     <t>Schedule Engine  |  Monthly Progress Dashboard</t>
   </si>
   <si>
-    <t>Industrial Plant Expansion - Phase 2 (Demo)   |   Data Date: 01-Oct-2026   |   Generated 26/9/2026, 7:53:48 pm by Schedule Engine</t>
+    <t>Industrial Plant Expansion - Phase 2 (Demo)   |   Data Date: 01-Oct-2026   |   Generated 28/9/2026, 9:07:00 am by Schedule Engine</t>
   </si>
   <si>
     <t>KEY FIGURES</t>
@@ -406,7 +407,7 @@
     <t>Finishes - flooring &amp; painting</t>
   </si>
   <si>
-    <t>Overdue, Due this period, In progress</t>
+    <t>Overdue, Due this period, In progress, No concern yet</t>
   </si>
   <si>
     <t>ADM-C1180</t>
@@ -550,7 +551,7 @@
     <t>WHS-C1140</t>
   </si>
   <si>
-    <t>Late start, Due this period, Pending update</t>
+    <t>Late start, Due this period, Pending update, No concern yet</t>
   </si>
   <si>
     <t>WHS-C1160</t>
@@ -667,7 +668,7 @@
     <t>UTL-P1070</t>
   </si>
   <si>
-    <t>Overdue, Due this period, In progress, Pending update</t>
+    <t>Overdue, Due this period, In progress, Pending update, No concern yet</t>
   </si>
   <si>
     <t>UTL-P1080</t>
@@ -739,7 +740,7 @@
     <t>STP-P1070</t>
   </si>
   <si>
-    <t>Late start, Overdue, Due this period, Pending update</t>
+    <t>Late start, Overdue, Due this period, Pending update, No concern yet</t>
   </si>
   <si>
     <t>STP-P1080</t>
@@ -760,7 +761,7 @@
     <t>STP-C1150</t>
   </si>
   <si>
-    <t>Future progress, In progress, Pending update, Out of sequence</t>
+    <t>Future progress, In progress, Pending update, Out of sequence, No concern yet</t>
   </si>
   <si>
     <t>STP-C1160</t>
@@ -1018,7 +1019,7 @@
     <t>4-8 weeks</t>
   </si>
   <si>
-    <t>Activities needing attention</t>
+    <t>Activities needing attention (flag + concern raised)</t>
   </si>
   <si>
     <t>Flag</t>
@@ -1033,25 +1034,37 @@
     <t>TF</t>
   </si>
   <si>
-    <t>Why flagged</t>
-  </si>
-  <si>
-    <t>Finish date (as per last update / plan) is before the Data Date but the activity is not complete.</t>
-  </si>
-  <si>
-    <t>Start date (as per last update / plan) is before the Data Date but no Actual Start yet.</t>
+    <t>Concern category</t>
+  </si>
+  <si>
+    <t>Concern</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>NOT RAISED</t>
   </si>
   <si>
     <t>Future progress</t>
   </si>
   <si>
-    <t>Planned to start after the Data Date but already has progress - verify it really started.</t>
-  </si>
-  <si>
     <t>Out of sequence</t>
   </si>
   <si>
-    <t>Started/finished before its predecessors allow.</t>
+    <t>Concerns register - 0 concerns as of 01-Oct-2026</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Target date</t>
+  </si>
+  <si>
+    <t>Raised</t>
   </si>
   <si>
     <t>Schedule health check - score 46%</t>
@@ -1347,7 +1360,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1445,6 +1458,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6007E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF483698"/>
       </patternFill>
     </fill>
@@ -1504,7 +1522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
@@ -1643,6 +1661,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2891,7 +2912,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{744BA967-8A2B-4619-ABC9-E4366C54A6BE}</x14:id>
+          <x14:id>{477AEEBF-9112-4A83-96EE-6C8C3D22BBFA}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2905,7 +2926,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9BE80167-1BDE-4D04-9088-C72E30AC653B}</x14:id>
+          <x14:id>{30C8800E-545B-4F93-BF2B-F2A38DF7ABAB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2916,7 +2937,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{744BA967-8A2B-4619-ABC9-E4366C54A6BE}">
+          <x14:cfRule type="dataBar" id="{477AEEBF-9112-4A83-96EE-6C8C3D22BBFA}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -2929,7 +2950,7 @@
           <xm:sqref>G12:G18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9BE80167-1BDE-4D04-9088-C72E30AC653B}">
+          <x14:cfRule type="dataBar" id="{30C8800E-545B-4F93-BF2B-F2A38DF7ABAB}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -2950,6 +2971,1002 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF7F7F7F"/>
+  </sheetPr>
+  <dimension ref="A1:E59"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="44" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="91" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="91" t="s">
+        <v>382</v>
+      </c>
+      <c r="E4" s="91" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="28">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>384</v>
+      </c>
+      <c r="E6" s="28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="E7" s="28">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>386</v>
+      </c>
+      <c r="E10" s="28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>387</v>
+      </c>
+      <c r="E11" s="28">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="E12" s="28">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="28">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>389</v>
+      </c>
+      <c r="E14" s="28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="28">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="28">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="28">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="28">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>384</v>
+      </c>
+      <c r="E19" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="E20" s="28">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="E22" s="28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="E27" s="28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>389</v>
+      </c>
+      <c r="E28" s="28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="E29" s="28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="28">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" s="28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" s="28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E41" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E46" s="28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="B47" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" s="28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="B57" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="B58" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E58" s="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="28">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E4"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF470A68"/>
   </sheetPr>
   <dimension ref="A1:F160"/>
@@ -2965,7 +3982,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2984,23 +4001,23 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="91" t="s">
-        <v>391</v>
-      </c>
-      <c r="B4" s="91" t="s">
-        <v>392</v>
-      </c>
-      <c r="C4" s="91" t="s">
-        <v>393</v>
-      </c>
-      <c r="D4" s="91" t="s">
-        <v>394</v>
-      </c>
-      <c r="E4" s="91" t="s">
+      <c r="A4" s="92" t="s">
         <v>395</v>
       </c>
-      <c r="F4" s="91" t="s">
+      <c r="B4" s="92" t="s">
         <v>396</v>
+      </c>
+      <c r="C4" s="92" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="92" t="s">
+        <v>398</v>
+      </c>
+      <c r="E4" s="92" t="s">
+        <v>399</v>
+      </c>
+      <c r="F4" s="92" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
@@ -3011,7 +4028,7 @@
         <v>82</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D5" s="28">
         <v>0</v>
@@ -3031,7 +4048,7 @@
         <v>92</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D6" s="28">
         <v>5</v>
@@ -3051,7 +4068,7 @@
         <v>92</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D7" s="28">
         <v>0</v>
@@ -3071,7 +4088,7 @@
         <v>94</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D8" s="28">
         <v>0</v>
@@ -3091,7 +4108,7 @@
         <v>96</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D9" s="28">
         <v>0</v>
@@ -3111,7 +4128,7 @@
         <v>94</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D10" s="28">
         <v>0</v>
@@ -3131,7 +4148,7 @@
         <v>101</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D11" s="28">
         <v>0</v>
@@ -3151,7 +4168,7 @@
         <v>96</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D12" s="28">
         <v>0</v>
@@ -3171,7 +4188,7 @@
         <v>105</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D13" s="28">
         <v>0</v>
@@ -3191,7 +4208,7 @@
         <v>82</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D14" s="28">
         <v>0</v>
@@ -3211,7 +4228,7 @@
         <v>111</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D15" s="28">
         <v>0</v>
@@ -3231,7 +4248,7 @@
         <v>94</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D16" s="28">
         <v>10</v>
@@ -3251,7 +4268,7 @@
         <v>113</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D17" s="28">
         <v>7</v>
@@ -3271,7 +4288,7 @@
         <v>115</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D18" s="28">
         <v>0</v>
@@ -3291,7 +4308,7 @@
         <v>117</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D19" s="28">
         <v>0</v>
@@ -3311,7 +4328,7 @@
         <v>103</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D20" s="28">
         <v>15</v>
@@ -3331,7 +4348,7 @@
         <v>119</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D21" s="28">
         <v>-5</v>
@@ -3351,7 +4368,7 @@
         <v>119</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D22" s="28">
         <v>20</v>
@@ -3371,7 +4388,7 @@
         <v>121</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D23" s="28">
         <v>10</v>
@@ -3391,7 +4408,7 @@
         <v>107</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D24" s="28">
         <v>0</v>
@@ -3411,7 +4428,7 @@
         <v>121</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D25" s="28">
         <v>0</v>
@@ -3431,7 +4448,7 @@
         <v>123</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D26" s="28">
         <v>0</v>
@@ -3451,7 +4468,7 @@
         <v>125</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D27" s="28">
         <v>0</v>
@@ -3471,7 +4488,7 @@
         <v>127</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D28" s="28">
         <v>0</v>
@@ -3491,7 +4508,7 @@
         <v>130</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D29" s="28">
         <v>0</v>
@@ -3511,7 +4528,7 @@
         <v>132</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D30" s="28">
         <v>0</v>
@@ -3531,7 +4548,7 @@
         <v>82</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D31" s="28">
         <v>10</v>
@@ -3551,7 +4568,7 @@
         <v>92</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D32" s="28">
         <v>5</v>
@@ -3571,7 +4588,7 @@
         <v>92</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D33" s="28">
         <v>0</v>
@@ -3591,7 +4608,7 @@
         <v>94</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D34" s="28">
         <v>0</v>
@@ -3611,7 +4628,7 @@
         <v>96</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D35" s="28">
         <v>0</v>
@@ -3631,7 +4648,7 @@
         <v>94</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D36" s="28">
         <v>0</v>
@@ -3651,7 +4668,7 @@
         <v>101</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D37" s="28">
         <v>0</v>
@@ -3671,7 +4688,7 @@
         <v>96</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D38" s="28">
         <v>0</v>
@@ -3691,7 +4708,7 @@
         <v>105</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D39" s="28">
         <v>0</v>
@@ -3711,7 +4728,7 @@
         <v>82</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D40" s="28">
         <v>10</v>
@@ -3731,7 +4748,7 @@
         <v>111</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D41" s="28">
         <v>0</v>
@@ -3751,7 +4768,7 @@
         <v>94</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D42" s="28">
         <v>10</v>
@@ -3771,7 +4788,7 @@
         <v>113</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D43" s="28">
         <v>7</v>
@@ -3791,7 +4808,7 @@
         <v>115</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D44" s="28">
         <v>0</v>
@@ -3811,7 +4828,7 @@
         <v>117</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D45" s="28">
         <v>0</v>
@@ -3831,7 +4848,7 @@
         <v>103</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D46" s="28">
         <v>15</v>
@@ -3851,7 +4868,7 @@
         <v>119</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D47" s="28">
         <v>-5</v>
@@ -3871,7 +4888,7 @@
         <v>119</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D48" s="28">
         <v>20</v>
@@ -3891,7 +4908,7 @@
         <v>121</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D49" s="28">
         <v>10</v>
@@ -3911,7 +4928,7 @@
         <v>107</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D50" s="28">
         <v>0</v>
@@ -3931,7 +4948,7 @@
         <v>121</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D51" s="28">
         <v>0</v>
@@ -3951,7 +4968,7 @@
         <v>123</v>
       </c>
       <c r="C52" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D52" s="28">
         <v>0</v>
@@ -3971,7 +4988,7 @@
         <v>125</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D53" s="28">
         <v>0</v>
@@ -3991,7 +5008,7 @@
         <v>127</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D54" s="28">
         <v>0</v>
@@ -4011,7 +5028,7 @@
         <v>130</v>
       </c>
       <c r="C55" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D55" s="28">
         <v>0</v>
@@ -4031,7 +5048,7 @@
         <v>132</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D56" s="28">
         <v>0</v>
@@ -4051,7 +5068,7 @@
         <v>82</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D57" s="28">
         <v>40</v>
@@ -4071,7 +5088,7 @@
         <v>92</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D58" s="28">
         <v>5</v>
@@ -4091,7 +5108,7 @@
         <v>92</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D59" s="28">
         <v>0</v>
@@ -4111,7 +5128,7 @@
         <v>94</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D60" s="28">
         <v>0</v>
@@ -4131,7 +5148,7 @@
         <v>96</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D61" s="28">
         <v>0</v>
@@ -4151,7 +5168,7 @@
         <v>94</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D62" s="28">
         <v>0</v>
@@ -4171,7 +5188,7 @@
         <v>101</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D63" s="28">
         <v>0</v>
@@ -4191,7 +5208,7 @@
         <v>96</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D64" s="28">
         <v>0</v>
@@ -4211,7 +5228,7 @@
         <v>105</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D65" s="28">
         <v>0</v>
@@ -4231,7 +5248,7 @@
         <v>82</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D66" s="28">
         <v>40</v>
@@ -4251,7 +5268,7 @@
         <v>111</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D67" s="28">
         <v>0</v>
@@ -4271,7 +5288,7 @@
         <v>94</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D68" s="28">
         <v>10</v>
@@ -4291,7 +5308,7 @@
         <v>113</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D69" s="28">
         <v>7</v>
@@ -4311,7 +5328,7 @@
         <v>115</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D70" s="28">
         <v>0</v>
@@ -4331,7 +5348,7 @@
         <v>117</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D71" s="28">
         <v>0</v>
@@ -4351,7 +5368,7 @@
         <v>103</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D72" s="28">
         <v>15</v>
@@ -4371,7 +5388,7 @@
         <v>119</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D73" s="28">
         <v>-5</v>
@@ -4391,7 +5408,7 @@
         <v>119</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D74" s="28">
         <v>20</v>
@@ -4411,7 +5428,7 @@
         <v>121</v>
       </c>
       <c r="C75" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D75" s="28">
         <v>10</v>
@@ -4431,7 +5448,7 @@
         <v>107</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D76" s="28">
         <v>0</v>
@@ -4451,7 +5468,7 @@
         <v>121</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D77" s="28">
         <v>0</v>
@@ -4471,7 +5488,7 @@
         <v>123</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D78" s="28">
         <v>0</v>
@@ -4491,7 +5508,7 @@
         <v>125</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D79" s="28">
         <v>0</v>
@@ -4511,7 +5528,7 @@
         <v>127</v>
       </c>
       <c r="C80" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D80" s="28">
         <v>0</v>
@@ -4531,7 +5548,7 @@
         <v>130</v>
       </c>
       <c r="C81" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D81" s="28">
         <v>0</v>
@@ -4551,7 +5568,7 @@
         <v>132</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D82" s="28">
         <v>0</v>
@@ -4571,7 +5588,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D83" s="28">
         <v>60</v>
@@ -4591,7 +5608,7 @@
         <v>92</v>
       </c>
       <c r="C84" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D84" s="28">
         <v>5</v>
@@ -4611,7 +5628,7 @@
         <v>92</v>
       </c>
       <c r="C85" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D85" s="28">
         <v>0</v>
@@ -4631,7 +5648,7 @@
         <v>94</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D86" s="28">
         <v>0</v>
@@ -4651,7 +5668,7 @@
         <v>96</v>
       </c>
       <c r="C87" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D87" s="28">
         <v>0</v>
@@ -4671,7 +5688,7 @@
         <v>94</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D88" s="28">
         <v>0</v>
@@ -4691,7 +5708,7 @@
         <v>101</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D89" s="28">
         <v>0</v>
@@ -4711,7 +5728,7 @@
         <v>96</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D90" s="28">
         <v>0</v>
@@ -4731,7 +5748,7 @@
         <v>105</v>
       </c>
       <c r="C91" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D91" s="28">
         <v>0</v>
@@ -4751,7 +5768,7 @@
         <v>82</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D92" s="28">
         <v>60</v>
@@ -4771,7 +5788,7 @@
         <v>111</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D93" s="28">
         <v>0</v>
@@ -4791,7 +5808,7 @@
         <v>94</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D94" s="28">
         <v>10</v>
@@ -4811,7 +5828,7 @@
         <v>113</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D95" s="28">
         <v>7</v>
@@ -4831,7 +5848,7 @@
         <v>115</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D96" s="28">
         <v>0</v>
@@ -4851,7 +5868,7 @@
         <v>117</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D97" s="28">
         <v>0</v>
@@ -4871,7 +5888,7 @@
         <v>103</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D98" s="28">
         <v>15</v>
@@ -4891,7 +5908,7 @@
         <v>119</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D99" s="28">
         <v>-5</v>
@@ -4911,7 +5928,7 @@
         <v>119</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D100" s="28">
         <v>20</v>
@@ -4931,7 +5948,7 @@
         <v>121</v>
       </c>
       <c r="C101" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D101" s="28">
         <v>10</v>
@@ -4951,7 +5968,7 @@
         <v>107</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D102" s="28">
         <v>0</v>
@@ -4971,7 +5988,7 @@
         <v>121</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D103" s="28">
         <v>0</v>
@@ -4991,7 +6008,7 @@
         <v>123</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D104" s="28">
         <v>0</v>
@@ -5011,7 +6028,7 @@
         <v>125</v>
       </c>
       <c r="C105" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D105" s="28">
         <v>0</v>
@@ -5031,7 +6048,7 @@
         <v>127</v>
       </c>
       <c r="C106" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D106" s="28">
         <v>0</v>
@@ -5051,7 +6068,7 @@
         <v>130</v>
       </c>
       <c r="C107" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D107" s="28">
         <v>0</v>
@@ -5071,7 +6088,7 @@
         <v>132</v>
       </c>
       <c r="C108" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D108" s="28">
         <v>0</v>
@@ -5091,7 +6108,7 @@
         <v>82</v>
       </c>
       <c r="C109" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D109" s="28">
         <v>90</v>
@@ -5111,7 +6128,7 @@
         <v>92</v>
       </c>
       <c r="C110" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D110" s="28">
         <v>5</v>
@@ -5131,7 +6148,7 @@
         <v>92</v>
       </c>
       <c r="C111" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D111" s="28">
         <v>0</v>
@@ -5151,7 +6168,7 @@
         <v>94</v>
       </c>
       <c r="C112" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D112" s="28">
         <v>0</v>
@@ -5171,7 +6188,7 @@
         <v>96</v>
       </c>
       <c r="C113" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D113" s="28">
         <v>0</v>
@@ -5191,7 +6208,7 @@
         <v>94</v>
       </c>
       <c r="C114" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D114" s="28">
         <v>0</v>
@@ -5211,7 +6228,7 @@
         <v>101</v>
       </c>
       <c r="C115" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D115" s="28">
         <v>0</v>
@@ -5231,7 +6248,7 @@
         <v>96</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D116" s="28">
         <v>0</v>
@@ -5251,7 +6268,7 @@
         <v>105</v>
       </c>
       <c r="C117" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D117" s="28">
         <v>0</v>
@@ -5271,7 +6288,7 @@
         <v>82</v>
       </c>
       <c r="C118" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D118" s="28">
         <v>90</v>
@@ -5291,7 +6308,7 @@
         <v>111</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D119" s="28">
         <v>0</v>
@@ -5311,7 +6328,7 @@
         <v>94</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D120" s="28">
         <v>10</v>
@@ -5331,7 +6348,7 @@
         <v>113</v>
       </c>
       <c r="C121" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D121" s="28">
         <v>7</v>
@@ -5351,7 +6368,7 @@
         <v>115</v>
       </c>
       <c r="C122" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D122" s="28">
         <v>0</v>
@@ -5371,7 +6388,7 @@
         <v>117</v>
       </c>
       <c r="C123" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D123" s="28">
         <v>0</v>
@@ -5391,7 +6408,7 @@
         <v>103</v>
       </c>
       <c r="C124" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D124" s="28">
         <v>15</v>
@@ -5411,7 +6428,7 @@
         <v>119</v>
       </c>
       <c r="C125" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D125" s="28">
         <v>-5</v>
@@ -5431,7 +6448,7 @@
         <v>119</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D126" s="28">
         <v>20</v>
@@ -5451,7 +6468,7 @@
         <v>121</v>
       </c>
       <c r="C127" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D127" s="28">
         <v>10</v>
@@ -5471,7 +6488,7 @@
         <v>107</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D128" s="28">
         <v>0</v>
@@ -5491,7 +6508,7 @@
         <v>121</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D129" s="28">
         <v>0</v>
@@ -5511,7 +6528,7 @@
         <v>123</v>
       </c>
       <c r="C130" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D130" s="28">
         <v>0</v>
@@ -5531,7 +6548,7 @@
         <v>125</v>
       </c>
       <c r="C131" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D131" s="28">
         <v>0</v>
@@ -5551,7 +6568,7 @@
         <v>127</v>
       </c>
       <c r="C132" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D132" s="28">
         <v>0</v>
@@ -5571,7 +6588,7 @@
         <v>130</v>
       </c>
       <c r="C133" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D133" s="28">
         <v>0</v>
@@ -5591,7 +6608,7 @@
         <v>132</v>
       </c>
       <c r="C134" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D134" s="28">
         <v>0</v>
@@ -5611,7 +6628,7 @@
         <v>82</v>
       </c>
       <c r="C135" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D135" s="28">
         <v>120</v>
@@ -5631,7 +6648,7 @@
         <v>92</v>
       </c>
       <c r="C136" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D136" s="28">
         <v>5</v>
@@ -5651,7 +6668,7 @@
         <v>92</v>
       </c>
       <c r="C137" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D137" s="28">
         <v>0</v>
@@ -5671,7 +6688,7 @@
         <v>94</v>
       </c>
       <c r="C138" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D138" s="28">
         <v>0</v>
@@ -5691,7 +6708,7 @@
         <v>96</v>
       </c>
       <c r="C139" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D139" s="28">
         <v>0</v>
@@ -5711,7 +6728,7 @@
         <v>94</v>
       </c>
       <c r="C140" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D140" s="28">
         <v>0</v>
@@ -5731,7 +6748,7 @@
         <v>101</v>
       </c>
       <c r="C141" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D141" s="28">
         <v>0</v>
@@ -5751,7 +6768,7 @@
         <v>96</v>
       </c>
       <c r="C142" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D142" s="28">
         <v>0</v>
@@ -5771,7 +6788,7 @@
         <v>105</v>
       </c>
       <c r="C143" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D143" s="28">
         <v>0</v>
@@ -5791,7 +6808,7 @@
         <v>82</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D144" s="28">
         <v>120</v>
@@ -5811,7 +6828,7 @@
         <v>111</v>
       </c>
       <c r="C145" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D145" s="28">
         <v>0</v>
@@ -5831,7 +6848,7 @@
         <v>94</v>
       </c>
       <c r="C146" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D146" s="28">
         <v>10</v>
@@ -5851,7 +6868,7 @@
         <v>113</v>
       </c>
       <c r="C147" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D147" s="28">
         <v>7</v>
@@ -5871,7 +6888,7 @@
         <v>115</v>
       </c>
       <c r="C148" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D148" s="28">
         <v>0</v>
@@ -5891,7 +6908,7 @@
         <v>117</v>
       </c>
       <c r="C149" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D149" s="28">
         <v>0</v>
@@ -5911,7 +6928,7 @@
         <v>103</v>
       </c>
       <c r="C150" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D150" s="28">
         <v>15</v>
@@ -5931,7 +6948,7 @@
         <v>119</v>
       </c>
       <c r="C151" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D151" s="28">
         <v>-5</v>
@@ -5951,7 +6968,7 @@
         <v>119</v>
       </c>
       <c r="C152" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D152" s="28">
         <v>20</v>
@@ -5971,7 +6988,7 @@
         <v>121</v>
       </c>
       <c r="C153" s="28" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D153" s="28">
         <v>10</v>
@@ -5991,7 +7008,7 @@
         <v>107</v>
       </c>
       <c r="C154" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D154" s="28">
         <v>0</v>
@@ -6011,7 +7028,7 @@
         <v>121</v>
       </c>
       <c r="C155" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D155" s="28">
         <v>0</v>
@@ -6031,7 +7048,7 @@
         <v>123</v>
       </c>
       <c r="C156" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D156" s="28">
         <v>0</v>
@@ -6051,7 +7068,7 @@
         <v>125</v>
       </c>
       <c r="C157" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D157" s="28">
         <v>0</v>
@@ -6071,7 +7088,7 @@
         <v>127</v>
       </c>
       <c r="C158" s="28" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D158" s="28">
         <v>0</v>
@@ -6091,7 +7108,7 @@
         <v>130</v>
       </c>
       <c r="C159" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D159" s="28">
         <v>0</v>
@@ -6111,7 +7128,7 @@
         <v>132</v>
       </c>
       <c r="C160" s="28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D160" s="28">
         <v>0</v>
@@ -31555,7 +32572,7 @@
   <sheetPr>
     <tabColor rgb="FFBC204B"/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -31566,10 +32583,13 @@
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="10" width="11" customWidth="1"/>
     <col min="11" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="60" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="60" customWidth="1"/>
+    <col min="15" max="15" width="40" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>332</v>
       </c>
@@ -31585,8 +32605,11 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -31602,8 +32625,11 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="88" t="s">
         <v>333</v>
       </c>
@@ -31643,8 +32669,17 @@
       <c r="M4" s="88" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N4" s="88" t="s">
+        <v>338</v>
+      </c>
+      <c r="O4" s="88" t="s">
+        <v>339</v>
+      </c>
+      <c r="P4" s="88" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>13</v>
       </c>
@@ -31682,10 +32717,19 @@
         <v>179</v>
       </c>
       <c r="M5" s="28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N5" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O5" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P5" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>13</v>
       </c>
@@ -31723,10 +32767,19 @@
         <v>79</v>
       </c>
       <c r="M6" s="28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N6" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O6" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P6" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>12</v>
       </c>
@@ -31764,10 +32817,19 @@
         <v>116</v>
       </c>
       <c r="M7" s="28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O7" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P7" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>13</v>
       </c>
@@ -31805,10 +32867,19 @@
         <v>99</v>
       </c>
       <c r="M8" s="28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N8" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O8" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P8" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>13</v>
       </c>
@@ -31846,10 +32917,19 @@
         <v>83</v>
       </c>
       <c r="M9" s="28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O9" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P9" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>12</v>
       </c>
@@ -31887,10 +32967,19 @@
         <v>118</v>
       </c>
       <c r="M10" s="28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N10" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O10" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>13</v>
       </c>
@@ -31928,10 +33017,19 @@
         <v>11</v>
       </c>
       <c r="M11" s="28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N11" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O11" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P11" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>12</v>
       </c>
@@ -31969,10 +33067,19 @@
         <v>11</v>
       </c>
       <c r="M12" s="28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N12" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O12" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P12" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>12</v>
       </c>
@@ -32010,10 +33117,19 @@
         <v>61</v>
       </c>
       <c r="M13" s="28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N13" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O13" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P13" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>12</v>
       </c>
@@ -32051,10 +33167,19 @@
         <v>86</v>
       </c>
       <c r="M14" s="28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N14" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O14" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P14" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>13</v>
       </c>
@@ -32092,10 +33217,19 @@
         <v>51</v>
       </c>
       <c r="M15" s="28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N15" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P15" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
         <v>13</v>
       </c>
@@ -32133,10 +33267,19 @@
         <v>151</v>
       </c>
       <c r="M16" s="28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N16" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O16" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P16" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
         <v>13</v>
       </c>
@@ -32174,10 +33317,19 @@
         <v>62</v>
       </c>
       <c r="M17" s="28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N17" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O17" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P17" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>12</v>
       </c>
@@ -32215,10 +33367,19 @@
         <v>62</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N18" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O18" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P18" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>12</v>
       </c>
@@ -32256,10 +33417,19 @@
         <v>62</v>
       </c>
       <c r="M19" s="28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N19" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O19" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P19" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>13</v>
       </c>
@@ -32297,10 +33467,19 @@
         <v>72</v>
       </c>
       <c r="M20" s="28" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N20" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O20" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P20" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
         <v>12</v>
       </c>
@@ -32338,12 +33517,21 @@
         <v>72</v>
       </c>
       <c r="M21" s="28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N21" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O21" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P21" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B22" s="28" t="s">
         <v>245</v>
@@ -32379,12 +33567,21 @@
         <v>76</v>
       </c>
       <c r="M22" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="N22" s="28" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O22" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P22" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B23" s="28" t="s">
         <v>245</v>
@@ -32420,12 +33617,21 @@
         <v>76</v>
       </c>
       <c r="M23" s="28" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="N23" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O23" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P23" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B24" s="28" t="s">
         <v>247</v>
@@ -32461,12 +33667,21 @@
         <v>62</v>
       </c>
       <c r="M24" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="N24" s="28" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O24" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P24" s="28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B25" s="28" t="s">
         <v>247</v>
@@ -32502,11 +33717,126 @@
         <v>62</v>
       </c>
       <c r="M25" s="28" t="s">
-        <v>343</v>
+        <v>76</v>
+      </c>
+      <c r="N25" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="O25" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="P25" s="28" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M4"/>
+  <autoFilter ref="A4:P4"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFC6007E"/>
+  </sheetPr>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="70" customWidth="1"/>
+    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="7" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="89" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="89" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="89" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="89" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="89" t="s">
+        <v>345</v>
+      </c>
+      <c r="G4" s="89" t="s">
+        <v>338</v>
+      </c>
+      <c r="H4" s="89" t="s">
+        <v>339</v>
+      </c>
+      <c r="I4" s="89" t="s">
+        <v>340</v>
+      </c>
+      <c r="J4" s="89" t="s">
+        <v>346</v>
+      </c>
+      <c r="K4" s="89" t="s">
+        <v>347</v>
+      </c>
+      <c r="L4" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="89" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
@@ -32516,7 +33846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF483698"/>
@@ -32531,7 +33861,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -32550,31 +33880,31 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="90" t="s">
         <v>322</v>
       </c>
-      <c r="B4" s="89" t="s">
-        <v>345</v>
-      </c>
-      <c r="C4" s="89" t="s">
-        <v>346</v>
-      </c>
-      <c r="D4" s="89" t="s">
-        <v>347</v>
-      </c>
-      <c r="E4" s="89" t="s">
+      <c r="B4" s="90" t="s">
+        <v>349</v>
+      </c>
+      <c r="C4" s="90" t="s">
+        <v>350</v>
+      </c>
+      <c r="D4" s="90" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="90" t="s">
         <v>272</v>
       </c>
-      <c r="F4" s="89" t="s">
-        <v>348</v>
+      <c r="F4" s="90" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C5" s="28">
         <v>0</v>
@@ -32586,15 +33916,15 @@
         <v>0</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C6" s="28">
         <v>6</v>
@@ -32606,15 +33936,15 @@
         <v>3.8</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C7" s="28">
         <v>46</v>
@@ -32626,15 +33956,15 @@
         <v>29.5</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="B8" s="28" t="s">
         <v>357</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>353</v>
       </c>
       <c r="C8" s="28">
         <v>48</v>
@@ -32646,15 +33976,15 @@
         <v>69.2</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C9" s="28">
         <v>0</v>
@@ -32666,15 +33996,15 @@
         <v>0</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C10" s="28">
         <v>44</v>
@@ -32686,15 +34016,15 @@
         <v>80</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C11" s="28">
         <v>0</v>
@@ -32706,15 +34036,15 @@
         <v>0</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C12" s="28">
         <v>20</v>
@@ -32726,15 +34056,15 @@
         <v>36.4</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C13" s="28">
         <v>0</v>
@@ -32746,15 +34076,15 @@
         <v>0</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C14" s="28">
         <v>82</v>
@@ -32766,15 +34096,15 @@
         <v>97.6</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C15" s="28">
         <v>5</v>
@@ -32786,15 +34116,15 @@
         <v>9.1</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C16" s="28">
         <v>61</v>
@@ -32806,15 +34136,15 @@
         <v>72.6</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C17" s="28">
         <v>0</v>
@@ -32826,7 +34156,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -32838,1000 +34168,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF7F7F7F"/>
-  </sheetPr>
-  <dimension ref="A1:E59"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="70" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="90" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="90" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="90" t="s">
-        <v>378</v>
-      </c>
-      <c r="E4" s="90" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="28">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="E6" s="28">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="E7" s="28">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="28">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="28">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="E10" s="28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>383</v>
-      </c>
-      <c r="E11" s="28">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="E12" s="28">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="28">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="E14" s="28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="28">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="28">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="28">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="28">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="E19" s="28">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>386</v>
-      </c>
-      <c r="E20" s="28">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="28">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>387</v>
-      </c>
-      <c r="E22" s="28">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="28">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="28">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="28">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="28">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>388</v>
-      </c>
-      <c r="E27" s="28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="E28" s="28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>389</v>
-      </c>
-      <c r="E29" s="28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C31" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="28">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E32" s="28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="B35" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" s="28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E40" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="B43" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E43" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="B44" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="B45" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C45" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="B46" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" s="28">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="B47" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="28">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D48" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="B49" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D49" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E49" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="C50" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="C52" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D52" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D53" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="B54" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C54" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D54" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="B55" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="C55" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D55" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="B56" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="C56" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D56" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E56" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="B57" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E57" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="28" t="s">
-        <v>252</v>
-      </c>
-      <c r="B58" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C58" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D58" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E58" s="28">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="B59" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C59" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D59" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="28">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:E4"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>